--- a/docs/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/Unit_Test_Plan_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Software_Testing_Suite" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Software_Testing_Suite" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Software_Testing_Suite'!$A$1:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Software_Testing_Suite'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2029,8 +2029,128 @@
         </is>
       </c>
     </row>
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>React UI — Severity Normalization</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Mount ResultsPanel.tsx with mock finding containing 'CRITICAL' severity</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>normalizeSeverity() parses raw severity string</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Finding binned into the 'High / Critical' top tier visual group</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>React UI — PR Summary Fallbacks</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Mount PRSummaryPanel.tsx with missing release_notes array in payload</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Array.isArray() checks execute before .map()</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Component gracefully renders 'No release notes generated.' without crashing</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>React UI — PDF Export Button</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Click 'Download Full PDF Report' in Results Panel</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>react-to-print hook invoked targeting the reportRef DOM node</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Browser native print dialog opens; @media print CSS rules perfectly retain dark mode</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Celery Concurrency — macOS Apple Silicon</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Start Celery worker with --pool=solo flag and submit LangGraph request</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Parallel graph execution via asyncio occurs inside the single solo worker process</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Task completes successfully without SIGSEGV fork() collisions</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F51"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>